--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,297 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128358349</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörviken, Rörviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545693</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6963279</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128358341</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörviken, Rörviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545702</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6963228</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128358356</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92663</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörviken, Rörviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545409</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6963316</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128358349</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>128358356</v>
       </c>
       <c r="B7" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365741</v>
+        <v>128358349</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtsjön, Jmt</t>
+          <t>Rörviken, Rörviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545828.1620525816</v>
+        <v>545693</v>
       </c>
       <c r="R2" t="n">
-        <v>6963300.639780369</v>
+        <v>6963279</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,35 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Vincent Heldt Cassel</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Vincent Heldt Cassel</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>97365714</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545869.8866917413</v>
+        <v>545869</v>
       </c>
       <c r="R3" t="n">
-        <v>6963265.987674399</v>
+        <v>6963266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +840,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365737</v>
+        <v>104406691</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, Jmt</t>
+          <t>Ansjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545847.531716333</v>
+        <v>545516</v>
       </c>
       <c r="R4" t="n">
-        <v>6963291.758274185</v>
+        <v>6963458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,26 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Erik Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128358349</v>
+        <v>128358356</v>
       </c>
       <c r="B5" t="n">
-        <v>92792</v>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545693</v>
+        <v>545409</v>
       </c>
       <c r="R5" t="n">
-        <v>6963279</v>
+        <v>6963316</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,7 +1070,7 @@
         <v>128358341</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128358356</v>
+        <v>97365737</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,37 +1175,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545409</v>
+        <v>545847</v>
       </c>
       <c r="R7" t="n">
-        <v>6963316</v>
+        <v>6963292</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,15 +1249,231 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Vincent Heldt Cassel</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Vincent Heldt Cassel</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97365741</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545828</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6963300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97365686</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545939</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6963257</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>spår av</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48780-2023 artfynd.xlsx
+++ b/artfynd/A 48780-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104406691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358356</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358341</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365737</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365741</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,8 +1514,23 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365686</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>